--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/CF_M05_arch_eval_avg.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/CF_M05_arch_eval_avg.xlsx
@@ -504,6 +504,8 @@
         <v>0.8166</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -586,7 +588,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.887</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
